--- a/DATA/DISENO_EXPERIMENTAL/configuracion_experimentos.xlsx
+++ b/DATA/DISENO_EXPERIMENTAL/configuracion_experimentos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,6 +685,206 @@
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Exp05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MinMaxScaler</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>32</v>
+      </c>
+      <c r="I6" t="n">
+        <v>100</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>mse</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Exp06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MinMaxScaler</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>32</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>mse</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Exp07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MinMaxScaler</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I8" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>mse</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Exp08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MinMaxScaler</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>32</v>
+      </c>
+      <c r="I9" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>mse</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
